--- a/merge/StructureDefinition-bc-subscription-notification-bundle.xlsx
+++ b/merge/StructureDefinition-bc-subscription-notification-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T00:47:30+00:00</t>
+    <t>2026-03-25T21:32:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>86</v>
